--- a/协作/14-改动清单.xlsx
+++ b/协作/14-改动清单.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -599,6 +599,90 @@
         </is>
       </c>
       <c r="H3" t="inlineStr">
+        <is>
+          <t>已合并</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>改动-0003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>切片-0002</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>契约-0003</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>协作/**</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>归档层实例落库（26/28/29/30/31/32/33/34/36/37）、证据-0006</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>8a5c71d</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>负责人</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>已合并</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>改动-0004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>切片-0002</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>契约-0003</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>协作/26,27,归档/**</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>首次归档快照 快照-0001（dcg-tm-v3.4.zip，197 份文件，SHA256 f93cc611…）与证据-0007；标签 tm-v3.4</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>38e02f7</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>负责人</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>已合并</t>
         </is>

--- a/协作/14-改动清单.xlsx
+++ b/协作/14-改动清单.xlsx
@@ -83,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -100,6 +100,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -465,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -685,6 +686,48 @@
       <c r="H5" t="inlineStr">
         <is>
           <t>已合并</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>改动-0005</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>切片-0002</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>契约-0003</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>TEAMODEL.md</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>附录 B 版本历史按版本号排序（3.3 与 3.4 两行位置对调，内容不变）；便于交付给外部项目时阅读</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>3508ff6</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>负责人</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>已提交</t>
         </is>
       </c>
     </row>

--- a/协作/14-改动清单.xlsx
+++ b/协作/14-改动清单.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -690,42 +690,84 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>改动-0005</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>切片-0002</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>契约-0003</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>TEAMODEL.md</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>附录 B 版本历史按版本号排序（3.3 与 3.4 两行位置对调，内容不变）；便于交付给外部项目时阅读</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>3508ff6</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>负责人</t>
         </is>
       </c>
-      <c r="H6" s="10" t="inlineStr">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>改动-0006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>切片-0003</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>契约-0004</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TEAMODEL.md;协作/模板/**</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>协议升 v3.5 全角色全开；模板枚举对齐附件B 与已有取值</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>3f1aef4</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>架构契约</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -733,10 +775,10 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="H2:H121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="只能选择下拉里的值" type="list">
+    <dataValidation sqref="H2:H121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"草稿,已提交,评审中,已合并,已废弃"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="只能选择下拉里的值" type="list">
+    <dataValidation sqref="G2:G121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"负责人,产品,需求分析,架构契约,实现工程师,代码评审,专项评审,测试验证,集成发布"</formula1>
     </dataValidation>
   </dataValidations>

--- a/协作/14-改动清单.xlsx
+++ b/协作/14-改动清单.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -768,6 +768,48 @@
         </is>
       </c>
       <c r="H7" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>改动-0007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>切片-0003</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>契约-0005</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>协作/**（37+3 交付物与记录）;协作/归档/dcg-tm-v3.5.zip</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>按协议 v3.5 全开落地：补齐 14 份缺交付物、重写 01 画像为九角色全开、追加 15 类记录、生成证据-0008..0011、写入快照-0002</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>77fb43c</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>负责人</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>

--- a/协作/14-改动清单.xlsx
+++ b/协作/14-改动清单.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -810,6 +810,48 @@
         </is>
       </c>
       <c r="H8" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>改动-0008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>切片-0004</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>契约-0006</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TEAMODEL.md;协作/模板/**;docs/TEAMODEL_draft_v1.md;协作/**</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>协议与模板移出 DCG，改由 https://github.com/CL98K/TEAMODEL.git (tag tm-v3.5.1) 维护；DCG 保留记录与本地模板缓存（.gitignore 排除）</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0436ca2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>负责人</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>

--- a/协作/14-改动清单.xlsx
+++ b/协作/14-改动清单.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -854,6 +854,48 @@
       <c r="H9" t="inlineStr">
         <is>
           <t>已提交</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>改动-0009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>切片-0005</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>契约-0007</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>README.md</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>标题 DCG v2→DCG；删除「状态：v2 是单产物编译器…」段；§0 定位改为适配场景（0.1 适合 7 项 / 0.2 不适合 7 项 / 0.3 四条约束）</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>cbe8fbe</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>负责人</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>已合并</t>
         </is>
       </c>
     </row>

--- a/协作/14-改动清单.xlsx
+++ b/协作/14-改动清单.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -894,6 +894,48 @@
         </is>
       </c>
       <c r="H10" t="inlineStr">
+        <is>
+          <t>已合并</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>改动-0010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>切片-0006</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>契约-0008</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>README.md</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>开篇：一份 JSON schema → 用 JSONata 描述怎么转、编译成固化 Python；§0 主场景明确为任意数据结构转换并在 0.1 首行单列</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>7c4760d</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>负责人</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
         <is>
           <t>已合并</t>
         </is>

--- a/协作/14-改动清单.xlsx
+++ b/协作/14-改动清单.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -936,6 +936,48 @@
         </is>
       </c>
       <c r="H11" t="inlineStr">
+        <is>
+          <t>已合并</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>改动-0011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>切片-0007</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>契约-0009</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>README.md</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>删除「当前实测 / 引擎修订锚点 / §6 性能终值锚定」引用块；§0 只保留适配场景标题与主场景说明</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ba1410d</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>负责人</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
         <is>
           <t>已合并</t>
         </is>
